--- a/Uploads/1_new_698.xlsx
+++ b/Uploads/1_new_698.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="48">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,124 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى كانز ستار زيادة %10- 355 مل</t>
+    <t>دبوس كوكى كرانشى بارد - 700 جم</t>
+  </si>
+  <si>
+    <t>دبوس كوكى كرانشى حار - 700 جم</t>
+  </si>
+  <si>
+    <t>اجنحة كوكى كرانشى بارد - 700 جم</t>
+  </si>
+  <si>
+    <t>اجنحة كوكى كرانشى حار - 700 جم</t>
+  </si>
+  <si>
+    <t>دجاج كوكى كرانشى بارد + بطاطس - 12 قطعه</t>
+  </si>
+  <si>
+    <t>دجاج كوكى كرانشى حار + بطاطس حار - 12 قطعه</t>
+  </si>
+  <si>
+    <t>بانيه كوكى توابل شرقية بارد 20 قطعة - 1 كجم</t>
+  </si>
+  <si>
+    <t>بانيه كوكى توابل شرقية حار 20 قطعة - 1 كجم</t>
+  </si>
+  <si>
+    <t>أطياب صدور بانية عادى - 400 جم</t>
+  </si>
+  <si>
+    <t>أطياب صدور بانية حار - 400 جم</t>
+  </si>
+  <si>
+    <t>أطياب استربس عادى - 400 جم</t>
+  </si>
+  <si>
+    <t>أطياب استربس حار - 400 جم</t>
+  </si>
+  <si>
+    <t>أطياب ناجتس - 400 جم</t>
+  </si>
+  <si>
+    <t>ناجتس كوكى كرانشى 20 قطعة - 400 جم</t>
+  </si>
+  <si>
+    <t>بانيه كوكى كرانشى بارد 8 قطعة - 400 جم</t>
+  </si>
+  <si>
+    <t>بانيه كوكى كرانشى حار 8 قطعة - 400 جم</t>
+  </si>
+  <si>
+    <t>ستربس كوكى بارد - 1 كجم</t>
+  </si>
+  <si>
+    <t>ستربس كوكى حار - 1 كجم</t>
+  </si>
+  <si>
+    <t>ستربس كوكى بارد - 400 جم</t>
+  </si>
+  <si>
+    <t>ستربس كوكى حار - 400 جم</t>
+  </si>
+  <si>
+    <t>دجاج مقلى شيكيتيتا بارد 12 قطعة - 1 كجم</t>
+  </si>
+  <si>
+    <t>دجاج مقلى شيكيتيتا حار 12 قطعة - 1 كجم</t>
+  </si>
+  <si>
+    <t>بانية شيكيتيتا عادى - 400 جم</t>
+  </si>
+  <si>
+    <t>بانية شيكيتيتا حار - 400 جم</t>
+  </si>
+  <si>
+    <t>استربس شيكيتيتا عادى - 400 جم</t>
+  </si>
+  <si>
+    <t>استربس شيكيتيتا حار - 400 جم</t>
+  </si>
+  <si>
+    <t>شهد ناجتس - 400 جم</t>
+  </si>
+  <si>
+    <t>ناجتس كوكى توابل الشرقية كرانشى - 50 قطعه</t>
+  </si>
+  <si>
+    <t>برجر دجاج كوكى - 8 قطعه</t>
+  </si>
+  <si>
+    <t>برجر دجاج كوكى توابل الشرقية بارد - 1 كجم</t>
+  </si>
+  <si>
+    <t>بانيه كوكى كرانشى بارد - 20 قطعه</t>
+  </si>
+  <si>
+    <t>اجنحة دجاج شيكيتيتا عادى - 700 جم</t>
+  </si>
+  <si>
+    <t>اجنحة دجاج شيكيتيتا حار - 700 جم</t>
+  </si>
+  <si>
+    <t>استربس شيكيتيتا بارد - 1 كجم</t>
+  </si>
+  <si>
+    <t>استربس شيكيتيتا حار- 1 كجم</t>
+  </si>
+  <si>
+    <t>دجاج بانية الفرات بارد - 1 كجم</t>
+  </si>
+  <si>
+    <t>شهد وجبة دجاج مقلية حار + بطاطس هدية - 12 قطعه</t>
+  </si>
+  <si>
+    <t>شهد وجبة دجاج مقلية عادي + بطاطس هدية - 12 قطعه</t>
+  </si>
+  <si>
+    <t>تشيكيتيتا ناجتس - 400 جم</t>
+  </si>
+  <si>
+    <t>تشيكيتيتا ناجتس - 1 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +543,1362 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25899</v>
+        <v>6218</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>335</v>
+        <v>2644</v>
       </c>
       <c r="E2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>6218</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>6219</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2669</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>6219</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>133</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>6220</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2173</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6221</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2197</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>6221</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>6222</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2345</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>6222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>195</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>6223</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>2353</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>6223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>196</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>6224</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1401</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>6224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>117</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>6225</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1400</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>6225</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>6339</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2718</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>6339</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>6340</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2691</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>6340</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>6341</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>3073</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>6341</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>6342</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>3069</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>6342</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>6343</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2726</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>6343</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>114</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>6560</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>2100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>6560</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>87</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>6561</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>2018</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>6561</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>84</v>
+      </c>
+      <c r="E31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>6562</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>2081</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>6562</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>6565</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>2784</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>6565</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35">
+        <v>232</v>
+      </c>
+      <c r="E35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>6566</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>2808</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>6566</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>234</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>6799</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1972</v>
+      </c>
+      <c r="E38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>6799</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+      <c r="D39">
+        <v>116</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>6800</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1979</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>6800</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>116</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>7564</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1597</v>
+      </c>
+      <c r="E42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>7564</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>160</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>7565</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1565</v>
+      </c>
+      <c r="E44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>7565</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45">
+        <v>7</v>
+      </c>
+      <c r="D45">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>7566</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1245</v>
+      </c>
+      <c r="E46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>7566</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>69</v>
+      </c>
+      <c r="E47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>7568</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>1219</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>7568</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
+        <v>68</v>
+      </c>
+      <c r="E49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>7569</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>1892</v>
+      </c>
+      <c r="E50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>7569</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>105</v>
+      </c>
+      <c r="E51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>7570</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1864</v>
+      </c>
+      <c r="E52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>7570</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>104</v>
+      </c>
+      <c r="E53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>8238</v>
+      </c>
+      <c r="B54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>1338</v>
+      </c>
+      <c r="E54" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>8238</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>84</v>
+      </c>
+      <c r="E55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>10482</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>1550</v>
+      </c>
+      <c r="E56" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>10482</v>
+      </c>
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
+      </c>
+      <c r="D57">
+        <v>129</v>
+      </c>
+      <c r="E57" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>10484</v>
+      </c>
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>1633</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>10484</v>
+      </c>
+      <c r="B59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>109</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>10486</v>
+      </c>
+      <c r="B60" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>1491</v>
+      </c>
+      <c r="E60" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>10486</v>
+      </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
+      </c>
+      <c r="D61">
+        <v>124</v>
+      </c>
+      <c r="E61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>10488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>1978</v>
+      </c>
+      <c r="E62" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>10488</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>165</v>
+      </c>
+      <c r="E63" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>11253</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>1709</v>
+      </c>
+      <c r="E64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>11253</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>107</v>
+      </c>
+      <c r="E65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>11254</v>
+      </c>
+      <c r="B66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>1726</v>
+      </c>
+      <c r="E66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>11254</v>
+      </c>
+      <c r="B67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67">
+        <v>7</v>
+      </c>
+      <c r="D67">
+        <v>108</v>
+      </c>
+      <c r="E67" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>11258</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>2085</v>
+      </c>
+      <c r="E68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>11258</v>
+      </c>
+      <c r="B69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>261</v>
+      </c>
+      <c r="E69" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>11259</v>
+      </c>
+      <c r="B70" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>2084</v>
+      </c>
+      <c r="E70" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>11259</v>
+      </c>
+      <c r="B71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71">
+        <v>261</v>
+      </c>
+      <c r="E71" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>11260</v>
+      </c>
+      <c r="B72" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1331</v>
+      </c>
+      <c r="E72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>11260</v>
+      </c>
+      <c r="B73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73">
+        <v>7</v>
+      </c>
+      <c r="D73">
+        <v>111</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>20994</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>2456</v>
+      </c>
+      <c r="E74" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>20994</v>
+      </c>
+      <c r="B75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75">
+        <v>7</v>
+      </c>
+      <c r="D75">
+        <v>205</v>
+      </c>
+      <c r="E75" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>20995</v>
+      </c>
+      <c r="B76" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>2463</v>
+      </c>
+      <c r="E76" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>20995</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>205</v>
+      </c>
+      <c r="E77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>21814</v>
+      </c>
+      <c r="B78" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>1200</v>
+      </c>
+      <c r="E78" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>21814</v>
+      </c>
+      <c r="B79" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>67</v>
+      </c>
+      <c r="E79" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>21816</v>
+      </c>
+      <c r="B80" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>1452</v>
+      </c>
+      <c r="E80" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>21816</v>
+      </c>
+      <c r="B81" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>145</v>
+      </c>
+      <c r="E81" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_698.xlsx
+++ b/Uploads/1_new_698.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="45">
   <si>
     <t>Product ID</t>
   </si>
@@ -46,6 +46,9 @@
     <t>كنور فيجيتار حار - 35 جم</t>
   </si>
   <si>
+    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
+  </si>
+  <si>
     <t>كنور خلطة كفتة- 35 جم</t>
   </si>
   <si>
@@ -70,6 +73,15 @@
     <t>كنور فاين فودز  مرقة لحمة - 12 مكعب</t>
   </si>
   <si>
+    <t>كنور خلطه فيجيتار اكسترا كرسبي  - 55 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة بطاطس - 6 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطه 11 بهار - 6 جم</t>
+  </si>
+  <si>
     <t>كنور مرقة دجاج فورية ظرف 40كيس - 6 جم</t>
   </si>
   <si>
@@ -128,6 +140,9 @@
   </si>
   <si>
     <t>صابون لوكس بشرة مثالية - 165 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة المفروم عرض 50 % كمية اكثر  - 70 جم</t>
   </si>
   <si>
     <t>كنور فيجيتار حار حجم التوفير - 250 جم</t>
@@ -491,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -531,7 +546,7 @@
         <v>660</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -548,7 +563,7 @@
         <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -565,7 +580,7 @@
         <v>1560</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -582,7 +597,7 @@
         <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -599,7 +614,7 @@
         <v>660</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -616,12 +631,12 @@
         <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -630,15 +645,15 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1308</v>
+        <v>697.5</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -647,877 +662,1064 @@
         <v>3</v>
       </c>
       <c r="D9">
-        <v>218</v>
+        <v>38.75</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>440</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>876</v>
+        <v>348.75</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>146</v>
+        <v>1308</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>512</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>1584</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>512</v>
+        <v>440</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>132</v>
+        <v>876</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>1801</v>
+        <v>440</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>285</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>1880</v>
+        <v>512</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>1560</v>
+        <v>1584</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>1880</v>
+        <v>512</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D16">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>2331</v>
+        <v>1801</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>3609</v>
+        <v>1880</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1056</v>
+        <v>1560</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>3609</v>
+        <v>1880</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>3610</v>
+        <v>2331</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>1112</v>
+        <v>235</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
       </c>
       <c r="C21">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>139</v>
+        <v>1056</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>6575</v>
+        <v>3609</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>1090</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>6575</v>
+        <v>3610</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>109</v>
+        <v>1112</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>8283</v>
+        <v>3610</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D24">
-        <v>695</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>8283</v>
+        <v>5577</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>58</v>
+        <v>798</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>8284</v>
+        <v>5577</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>695</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>8284</v>
+        <v>5584</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>58</v>
+        <v>1115</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>8285</v>
+        <v>5584</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>695</v>
+        <v>111.5</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>8285</v>
+        <v>5585</v>
       </c>
       <c r="B29" t="s">
         <v>21</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>58</v>
+        <v>1090</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>8286</v>
+        <v>5585</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>695</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>8286</v>
+        <v>6575</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>58</v>
+        <v>1090</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>8753</v>
+        <v>6575</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>970</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>8753</v>
+        <v>8283</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>80.75</v>
+        <v>695</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>8754</v>
+        <v>8283</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>970</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>8754</v>
+        <v>8284</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>80.75</v>
+        <v>695</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>8756</v>
+        <v>8284</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>970</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>8756</v>
+        <v>8285</v>
       </c>
       <c r="B37" t="s">
         <v>25</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>80.75</v>
+        <v>695</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>9065</v>
+        <v>8285</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>735</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>9065</v>
+        <v>8286</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>92</v>
+        <v>695</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>9396</v>
+        <v>8286</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1205</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>9396</v>
+        <v>8753</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>150.5</v>
+        <v>970</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>9820</v>
+        <v>8753</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>792</v>
+        <v>80.75</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>9820</v>
+        <v>8754</v>
       </c>
       <c r="B43" t="s">
         <v>28</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>66</v>
+        <v>970</v>
       </c>
       <c r="E43" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>11226</v>
+        <v>8754</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>630</v>
+        <v>80.75</v>
       </c>
       <c r="E44" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>11467</v>
+        <v>8756</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45">
-        <v>285</v>
+        <v>970</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>11485</v>
+        <v>8756</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46">
-        <v>1040</v>
+        <v>80.75</v>
       </c>
       <c r="E46" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>11485</v>
+        <v>9065</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C47">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>130</v>
+        <v>735</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>11687</v>
+        <v>9065</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>735</v>
+        <v>92</v>
       </c>
       <c r="E48" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>11687</v>
+        <v>9396</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>92</v>
+        <v>1205</v>
       </c>
       <c r="E49" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>11689</v>
+        <v>9396</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>735</v>
+        <v>150.5</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>11689</v>
+        <v>9820</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>92</v>
+        <v>792</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>11690</v>
+        <v>9820</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52">
-        <v>735</v>
+        <v>66</v>
       </c>
       <c r="E52" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>11690</v>
+        <v>11226</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>92</v>
+        <v>630</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>11885</v>
+        <v>11467</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54">
-        <v>1205</v>
+        <v>285</v>
       </c>
       <c r="E54" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>11885</v>
+        <v>11485</v>
       </c>
       <c r="B55" t="s">
         <v>35</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>150.5</v>
+        <v>1040</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>11886</v>
+        <v>11485</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D56">
-        <v>1205</v>
+        <v>130</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>11886</v>
+        <v>11687</v>
       </c>
       <c r="B57" t="s">
         <v>36</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>150.5</v>
+        <v>735</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>11887</v>
+        <v>11687</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>1205</v>
+        <v>92</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>11887</v>
+        <v>11689</v>
       </c>
       <c r="B59" t="s">
         <v>37</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>150.5</v>
+        <v>735</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
+        <v>11689</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>92</v>
+      </c>
+      <c r="E60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>11690</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>735</v>
+      </c>
+      <c r="E61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>11690</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>92</v>
+      </c>
+      <c r="E62" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>11885</v>
+      </c>
+      <c r="B63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>1205</v>
+      </c>
+      <c r="E63" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>11885</v>
+      </c>
+      <c r="B64" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>150.5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>11886</v>
+      </c>
+      <c r="B65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>1205</v>
+      </c>
+      <c r="E65" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>11886</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>150.5</v>
+      </c>
+      <c r="E66" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>11887</v>
+      </c>
+      <c r="B67" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>1205</v>
+      </c>
+      <c r="E67" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>11887</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>150.5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>12010</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>1095</v>
+      </c>
+      <c r="E69" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>12010</v>
+      </c>
+      <c r="B70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>182.5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
         <v>12128</v>
       </c>
-      <c r="B60" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60">
+      <c r="B71" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
         <v>638</v>
       </c>
-      <c r="E60" t="s">
-        <v>39</v>
+      <c r="E71" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_698.xlsx
+++ b/Uploads/1_new_698.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="45">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,19 +37,115 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى مقاس 2 دبل لوك - 84 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+    <t>فجيتار كنور عادى - 35 جم</t>
+  </si>
+  <si>
+    <t>فاين فودز مرقة دجاج 8 مكعب- 72 جم</t>
+  </si>
+  <si>
+    <t>كنور فيجيتار حار - 35 جم</t>
+  </si>
+  <si>
+    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة كفتة- 35 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة بشاميل- 70 جم</t>
+  </si>
+  <si>
+    <t>كنور فاين فودز مرقة لحم البقر عبوه اقتصاديه 8 مكعب - 72 جم</t>
+  </si>
+  <si>
+    <t>شامبو كلير رجالى ازرق اخضر و اسود - 5 مل</t>
+  </si>
+  <si>
+    <t>فاين فودز مرقة خضار 8 مكعب- 72 جم</t>
+  </si>
+  <si>
+    <t>صانسيلك اكياس شامبو للشعر الاسود- 240 كيس 7 مل</t>
+  </si>
+  <si>
+    <t>كنور  مرقة خضروات عرض خاص- 12 مكعب</t>
+  </si>
+  <si>
+    <t>كنور فاين فودز مرقة لحمة عبوه اقتصاديه - 12 مكعب</t>
+  </si>
+  <si>
+    <t>كنور خلطه فيجيتار اكسترا كرسبي  - 55 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة بطاطس - 6 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطه 11 بهار - 6 جم</t>
+  </si>
+  <si>
+    <t>كنور مرقة دجاج فورية ظرف 40كيس - 6 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى اناقة -- 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى حيوية - 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى كلاسيك -- 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى اناقة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى كلاسيك - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 165 جم</t>
+  </si>
+  <si>
+    <t>لوكس صابون حلم السعادة  - 115 جم</t>
+  </si>
+  <si>
+    <t>لوكس صابون حلم السعاده / برتقالي - 165 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطه البرجر - 30 جم</t>
+  </si>
+  <si>
+    <t>كنور فيجيتار عادي حجم التوفير - 250 جم</t>
+  </si>
+  <si>
+    <t>شامبو كلير حريمى بامبى - 5 مل</t>
+  </si>
+  <si>
+    <t>كنور فاين فودز مرقة دجاج عرض خاص - 12 مكعب 108 جرام</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة مثالية - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة مثالية - 165 جم</t>
+  </si>
+  <si>
+    <t>كنور خلطة المفروم عرض 50 % كمية اكثر  - 70 جم</t>
+  </si>
+  <si>
+    <t>كنور فيجيتار حار حجم التوفير - 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -410,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,172 +534,1192 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9239</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>342</v>
+        <v>660</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>9239</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1027</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13256</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>351</v>
+        <v>1560</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>13256</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>703</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>13257</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>374</v>
+        <v>660</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>13257</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>749</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>13258</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>374</v>
+        <v>697.5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>13258</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>749</v>
+        <v>38.75</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>13259</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>417</v>
+        <v>348.75</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>13259</v>
+        <v>209</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1308</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>218</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>440</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>876</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>440</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>146</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>512</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1584</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>512</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>132</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>1801</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>285</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>1880</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1560</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>1880</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>2331</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>235</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>3609</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1056</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>3609</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>24</v>
+      </c>
+      <c r="D22">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>3610</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3610</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>24</v>
+      </c>
+      <c r="D24">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>5577</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>798</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>5577</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>5584</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1115</v>
+      </c>
+      <c r="E27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>5584</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>111.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>5585</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1090</v>
+      </c>
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>5585</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>6575</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1090</v>
+      </c>
+      <c r="E31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>6575</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>109</v>
+      </c>
+      <c r="E32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>8283</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>695</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>8283</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>8284</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>695</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>8284</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>58</v>
+      </c>
+      <c r="E36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>8285</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>695</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>8285</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>58</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>8286</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>695</v>
+      </c>
+      <c r="E39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>8286</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>58</v>
+      </c>
+      <c r="E40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>8753</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>970</v>
+      </c>
+      <c r="E41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>8753</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>80.75</v>
+      </c>
+      <c r="E42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>8754</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>970</v>
+      </c>
+      <c r="E43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>8754</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>80.75</v>
+      </c>
+      <c r="E44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>8756</v>
+      </c>
+      <c r="B45" t="s">
         <v>29</v>
       </c>
-      <c r="D11">
-        <v>835</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>970</v>
+      </c>
+      <c r="E45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>8756</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>80.75</v>
+      </c>
+      <c r="E46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>9065</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>735</v>
+      </c>
+      <c r="E47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>9065</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>92</v>
+      </c>
+      <c r="E48" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>9396</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>1205</v>
+      </c>
+      <c r="E49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>9396</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>150.5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>9820</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>792</v>
+      </c>
+      <c r="E51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>9820</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>66</v>
+      </c>
+      <c r="E52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>11226</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>630</v>
+      </c>
+      <c r="E53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>11467</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>285</v>
+      </c>
+      <c r="E54" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>11485</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1040</v>
+      </c>
+      <c r="E55" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>11485</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56">
+        <v>24</v>
+      </c>
+      <c r="D56">
+        <v>130</v>
+      </c>
+      <c r="E56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>11687</v>
+      </c>
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>735</v>
+      </c>
+      <c r="E57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>11687</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>92</v>
+      </c>
+      <c r="E58" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>11689</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>735</v>
+      </c>
+      <c r="E59" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>11689</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>92</v>
+      </c>
+      <c r="E60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>11690</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>735</v>
+      </c>
+      <c r="E61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>11690</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>92</v>
+      </c>
+      <c r="E62" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>11885</v>
+      </c>
+      <c r="B63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>1205</v>
+      </c>
+      <c r="E63" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>11885</v>
+      </c>
+      <c r="B64" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>150.5</v>
+      </c>
+      <c r="E64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>11886</v>
+      </c>
+      <c r="B65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>1205</v>
+      </c>
+      <c r="E65" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>11886</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66">
+        <v>150.5</v>
+      </c>
+      <c r="E66" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67">
+        <v>11887</v>
+      </c>
+      <c r="B67" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>1205</v>
+      </c>
+      <c r="E67" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>11887</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>150.5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>12010</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>1095</v>
+      </c>
+      <c r="E69" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>12010</v>
+      </c>
+      <c r="B70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>182.5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>12128</v>
+      </c>
+      <c r="B71" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>638</v>
+      </c>
+      <c r="E71" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
